--- a/data/trans_orig/IQ19B_A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ19B_A-Edad-trans_orig.xlsx
@@ -1916,7 +1916,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>5547</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -3179,12 +3179,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5993</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3214,12 +3214,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5525</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9311</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -3290,12 +3290,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20891</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>14155</t>
+          <t>14470</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21589</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>29859</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>40554</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3375,12 +3375,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -3401,12 +3401,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>11061</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3471,12 +3471,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>17345</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,16%</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>3663</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -4517,12 +4517,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>462</t>
+          <t>461</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4587,12 +4587,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>669</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5844</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1967</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>4316</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4713,12 +4713,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>23283</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>31081</t>
+          <t>31054</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>41465</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>53946</t>
+          <t>53157</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,01%</t>
         </is>
       </c>
     </row>
@@ -4850,12 +4850,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>6624</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4865,12 +4865,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1237</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>7132</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>3297</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -4935,12 +4935,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3315</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2664</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -5673,7 +5673,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5708,7 +5708,7 @@
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>4348</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5723,7 +5723,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4579</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>12379</t>
+          <t>12618</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17408</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>19566</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>34509</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>34120</t>
+          <t>33682</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>40338</t>
+          <t>40560</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>54990</t>
+          <t>55791</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>77026</t>
+          <t>78704</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>98106</t>
+          <t>97482</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,74%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>17336</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8658</t>
+          <t>8692</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>20066</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>17903</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>34036</t>
+          <t>33284</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6713,7 +6713,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -7309,7 +7309,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>4178</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>728</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -7415,12 +7415,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2541</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9895</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7430,12 +7430,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7450,12 +7450,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>5030</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>13949</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>9402</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>21163</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -7526,12 +7526,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13385</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26303</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>14265</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>28323</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31680</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>49469</t>
+          <t>50886</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -7637,12 +7637,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>70195</t>
+          <t>70293</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>88083</t>
+          <t>87670</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>83628</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>103253</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>159535</t>
+          <t>159202</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>184425</t>
+          <t>184346</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -7748,12 +7748,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>16873</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31521</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -7783,12 +7783,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>31496</t>
+          <t>30604</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7798,12 +7798,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7818,12 +7818,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37834</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>57477</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10635,7 +10635,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -10656,12 +10656,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10618</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10741,12 +10741,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -10767,12 +10767,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>7747</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>15909</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10782,12 +10782,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10802,12 +10802,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>13757</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>20242</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10817,12 +10817,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>34623</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -10878,12 +10878,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4593</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12317</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10913,12 +10913,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>655</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10948,12 +10948,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6628</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>15995</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2625</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11459,7 +11459,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -11812,7 +11812,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3242</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -11827,7 +11827,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>2911</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -11903,7 +11903,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -12034,7 +12034,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>3980</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -12064,12 +12064,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>598</t>
+          <t>600</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5495</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>12807</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>8537</t>
+          <t>8509</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>20209</t>
+          <t>19654</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -12216,12 +12216,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>24053</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>33812</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12231,12 +12231,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>76,53%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31401</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>43785</t>
+          <t>43431</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -12266,12 +12266,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -12286,12 +12286,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>58719</t>
+          <t>57940</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>74980</t>
+          <t>74973</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -12301,12 +12301,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -12327,12 +12327,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>10770</t>
+          <t>9958</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -12342,12 +12342,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -12362,12 +12362,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>9000</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>19837</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12377,12 +12377,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -12397,12 +12397,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>13219</t>
+          <t>13434</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>26979</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12412,12 +12412,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -12706,7 +12706,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4109</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>4187</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12963,7 +12963,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12978,7 +12978,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -13004,7 +13004,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>4624</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13115,7 +13115,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>8435</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -13130,7 +13130,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -13150,7 +13150,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -13165,7 +13165,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -13180,12 +13180,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>436</t>
+          <t>433</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>7503</t>
+          <t>7803</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -13256,12 +13256,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -13271,12 +13271,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -13291,12 +13291,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5835</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -13306,12 +13306,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -13332,12 +13332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -13372,7 +13372,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3492</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -13402,12 +13402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>862</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13417,12 +13417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -13443,12 +13443,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2835</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -13458,12 +13458,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -13478,12 +13478,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2596</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -13493,12 +13493,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -13513,12 +13513,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>17611</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -13528,12 +13528,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,89%</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5862</t>
+          <t>5762</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -13569,12 +13569,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -13589,12 +13589,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11268</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11091</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>23313</t>
+          <t>22925</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -13665,12 +13665,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>32661</t>
+          <t>32888</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46422</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -13680,12 +13680,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -13700,12 +13700,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>39269</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>51437</t>
+          <t>51607</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -13715,12 +13715,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>94013</t>
+          <t>93664</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -13776,12 +13776,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>11469</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13811,12 +13811,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11534</t>
+          <t>11408</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13826,12 +13826,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13846,12 +13846,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>19725</t>
+          <t>19389</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13861,12 +13861,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -14155,7 +14155,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -14357,7 +14357,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2633</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>464</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -14427,7 +14427,7 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4685</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -14564,7 +14564,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14614,7 +14614,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>430</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>7982</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14649,7 +14649,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14705,12 +14705,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>6365</t>
+          <t>7418</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14725,7 +14725,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14740,12 +14740,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>653</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14755,12 +14755,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -14781,12 +14781,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>7286</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14821,7 +14821,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14836,7 +14836,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14851,12 +14851,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1942</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -14892,12 +14892,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14907,12 +14907,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14927,12 +14927,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>12225</t>
+          <t>12519</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14942,12 +14942,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -14977,12 +14977,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -15003,12 +15003,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>15012</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>28816</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15018,12 +15018,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15038,12 +15038,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>20751</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -15053,12 +15053,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -15073,12 +15073,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>26575</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>45055</t>
+          <t>45398</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15088,12 +15088,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>73158</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>91704</t>
+          <t>91961</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -15149,12 +15149,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>91416</t>
+          <t>90049</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>109756</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -15164,12 +15164,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -15184,12 +15184,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>169937</t>
+          <t>168769</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>197016</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -15199,12 +15199,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -15225,12 +15225,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -15240,12 +15240,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -15260,12 +15260,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16485</t>
+          <t>15893</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>31148</t>
+          <t>31187</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -15275,12 +15275,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -15295,12 +15295,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>33871</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>54624</t>
+          <t>54409</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -15310,12 +15310,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -18168,12 +18168,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6827</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18183,12 +18183,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18203,12 +18203,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1186</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18218,12 +18218,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -18244,12 +18244,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12829</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19845</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18259,12 +18259,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18279,12 +18279,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19413</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18294,12 +18294,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -18314,12 +18314,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>37240</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18329,12 +18329,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10508</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18390,12 +18390,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11811</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18405,12 +18405,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18425,12 +18425,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>9663</t>
+          <t>10178</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>20017</t>
+          <t>20004</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18440,12 +18440,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -19047,7 +19047,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -19082,7 +19082,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -19117,7 +19117,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -19254,7 +19254,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -19269,7 +19269,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -19324,7 +19324,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>4354</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -19400,7 +19400,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3685</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -19415,7 +19415,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -19435,7 +19435,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5363</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -19450,7 +19450,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -19476,7 +19476,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3272</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -19511,7 +19511,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4482</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -19526,7 +19526,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -19541,12 +19541,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -19561,7 +19561,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -19582,12 +19582,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -19597,12 +19597,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -19617,12 +19617,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -19632,12 +19632,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -19652,12 +19652,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>12892</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>26085</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -19667,12 +19667,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -19693,12 +19693,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>37110</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>49931</t>
+          <t>49611</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -19708,12 +19708,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -19728,12 +19728,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>46857</t>
+          <t>46816</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -19743,12 +19743,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -19763,12 +19763,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>74321</t>
+          <t>75048</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>93392</t>
+          <t>93816</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -19778,12 +19778,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,6%</t>
         </is>
       </c>
     </row>
@@ -19804,12 +19804,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>7327</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>18235</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -19819,12 +19819,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -19839,12 +19839,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18060</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -19854,12 +19854,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -19874,12 +19874,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16489</t>
+          <t>16252</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>31460</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -19889,12 +19889,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -20738,7 +20738,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -20753,7 +20753,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -20773,7 +20773,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3826</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -20814,7 +20814,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>4406</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -20844,12 +20844,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>6791</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -20859,12 +20859,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>8848</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -20899,7 +20899,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -20920,12 +20920,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -20940,7 +20940,7 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -20955,12 +20955,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>6188</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -20970,12 +20970,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -20990,12 +20990,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2237</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -21005,12 +21005,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -21031,12 +21031,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>14557</t>
+          <t>14724</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -21046,12 +21046,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -21066,12 +21066,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>16835</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -21081,12 +21081,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -21101,12 +21101,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>13955</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>28180</t>
+          <t>28906</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -21116,12 +21116,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -21142,12 +21142,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>33759</t>
+          <t>33136</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>45250</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -21177,12 +21177,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>38705</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>52200</t>
+          <t>52061</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -21192,12 +21192,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -21212,12 +21212,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>75954</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>95185</t>
+          <t>94978</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -21227,12 +21227,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -21253,12 +21253,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>14148</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -21268,12 +21268,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -21288,12 +21288,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13205</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -21303,12 +21303,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -21323,12 +21323,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11459</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>24818</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -21930,7 +21930,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -21945,7 +21945,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3952</t>
+          <t>3233</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -22000,7 +22000,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>4126</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -22015,7 +22015,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4166</t>
+          <t>3380</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -22167,7 +22167,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -22222,7 +22222,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4625</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -22263,7 +22263,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22293,12 +22293,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22308,12 +22308,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22328,12 +22328,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>1418</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22343,12 +22343,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -22369,12 +22369,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1209</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>7096</t>
+          <t>7493</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22384,12 +22384,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22404,12 +22404,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>1340</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7690</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22419,12 +22419,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22454,12 +22454,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -22480,12 +22480,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>13374</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>27626</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -22495,12 +22495,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -22515,12 +22515,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16239</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>32327</t>
+          <t>30968</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22530,12 +22530,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22550,12 +22550,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>33083</t>
+          <t>32800</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>52933</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22565,12 +22565,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -22591,12 +22591,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>89325</t>
+          <t>89560</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>109473</t>
+          <t>108849</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
@@ -22626,12 +22626,12 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>92716</t>
+          <t>92387</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>113008</t>
+          <t>113344</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -22641,12 +22641,12 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -22661,12 +22661,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>187732</t>
+          <t>188300</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>216330</t>
+          <t>217145</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -22676,12 +22676,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>20835</t>
+          <t>20063</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -22717,12 +22717,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -22737,12 +22737,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>36048</t>
+          <t>34960</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -22752,12 +22752,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -22772,12 +22772,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>44720</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66458</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -22787,12 +22787,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -23459,7 +23459,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>43,84%</t>
         </is>
       </c>
     </row>
@@ -24070,7 +24070,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -24125,7 +24125,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -24140,7 +24140,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -24201,7 +24201,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -24216,7 +24216,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -24236,7 +24236,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -24251,7 +24251,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>63,79%</t>
         </is>
       </c>
     </row>
@@ -24272,12 +24272,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -24287,12 +24287,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -24342,12 +24342,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -24357,12 +24357,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -24388,7 +24388,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -24403,7 +24403,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -24438,7 +24438,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -24458,7 +24458,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2641</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -24473,7 +24473,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>54,9%</t>
         </is>
       </c>
     </row>
@@ -24651,7 +24651,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>5083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -24666,7 +24666,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -24686,7 +24686,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -24701,7 +24701,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -24873,7 +24873,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -24888,7 +24888,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -24908,7 +24908,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -24923,7 +24923,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -25206,7 +25206,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4181</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -25221,7 +25221,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -25256,7 +25256,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -25610,12 +25610,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7617</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -25645,12 +25645,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2744</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12806</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -25660,12 +25660,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16457</t>
+          <t>17083</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -25695,12 +25695,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -25721,12 +25721,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10633</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>19227</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -25736,12 +25736,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -25756,12 +25756,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>16516</t>
+          <t>16593</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>27839</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -25771,12 +25771,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -25791,12 +25791,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>30097</t>
+          <t>29560</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -25806,12 +25806,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>65,53%</t>
         </is>
       </c>
     </row>
@@ -25832,12 +25832,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5498</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -25847,12 +25847,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -25867,12 +25867,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4051</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12559</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -25882,12 +25882,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -25902,12 +25902,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>11785</t>
+          <t>11802</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>23528</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -25917,12 +25917,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,34%</t>
         </is>
       </c>
     </row>
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -26579,7 +26579,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -26594,7 +26594,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -26731,7 +26731,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -26816,7 +26816,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -26877,7 +26877,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -26912,7 +26912,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4496</t>
+          <t>4158</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -26927,7 +26927,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -26948,12 +26948,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>6482</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -26963,12 +26963,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -26988,7 +26988,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -27018,12 +27018,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -27033,12 +27033,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -27059,12 +27059,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>9312</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -27074,12 +27074,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -27094,12 +27094,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>13014</t>
+          <t>12687</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -27109,12 +27109,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -27129,12 +27129,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7070</t>
+          <t>6430</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -27144,12 +27144,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -27170,12 +27170,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>31952</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>46557</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -27185,12 +27185,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -27205,12 +27205,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>28764</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>45180</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -27220,12 +27220,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -27240,12 +27240,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>64750</t>
+          <t>65693</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>88105</t>
+          <t>87427</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -27255,12 +27255,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>47,79%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>63,61%</t>
         </is>
       </c>
     </row>
@@ -27281,12 +27281,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>25330</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -27296,12 +27296,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -27316,12 +27316,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>16508</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>33385</t>
+          <t>33866</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -27331,12 +27331,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -27351,12 +27351,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>32094</t>
+          <t>32489</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27366,12 +27366,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -27514,7 +27514,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -27529,7 +27529,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -27584,7 +27584,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -27599,7 +27599,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -27958,7 +27958,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>3827</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -27973,7 +27973,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -28028,7 +28028,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -28180,7 +28180,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -28195,7 +28195,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -28215,7 +28215,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>7539</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -28230,7 +28230,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -28250,7 +28250,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>9611</t>
+          <t>8329</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -28265,7 +28265,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -28397,12 +28397,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -28412,12 +28412,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -28432,12 +28432,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>831</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>8898</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -28452,7 +28452,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -28467,12 +28467,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2172</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -28482,12 +28482,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -28508,12 +28508,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>10676</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>22467</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -28523,12 +28523,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -28543,12 +28543,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>29822</t>
+          <t>29584</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -28558,12 +28558,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -28578,12 +28578,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>28195</t>
+          <t>28744</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>47579</t>
+          <t>48162</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -28593,12 +28593,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -28619,12 +28619,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>39234</t>
+          <t>39737</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>56270</t>
+          <t>56873</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -28634,12 +28634,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -28654,12 +28654,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>58462</t>
+          <t>58042</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>79764</t>
+          <t>79274</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -28669,12 +28669,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -28689,12 +28689,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>103474</t>
+          <t>102876</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>131375</t>
+          <t>130069</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -28704,12 +28704,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>58,12%</t>
         </is>
       </c>
     </row>
@@ -28730,12 +28730,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>22144</t>
+          <t>21921</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -28745,12 +28745,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>20230</t>
+          <t>21149</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40175</t>
+          <t>40665</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -28780,12 +28780,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -28800,12 +28800,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>47941</t>
+          <t>48370</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>73052</t>
+          <t>73656</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -28815,12 +28815,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,91%</t>
         </is>
       </c>
     </row>
@@ -28963,7 +28963,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>4465</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -29033,7 +29033,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -29185,7 +29185,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -29200,7 +29200,7 @@
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -29220,7 +29220,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -29255,7 +29255,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>7399</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -29407,7 +29407,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -29422,44 +29422,44 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>4740</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
           <t>1,98%</t>
         </is>
       </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>955</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>5261</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
           <t>2</t>
@@ -29477,7 +29477,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29492,7 +29492,7 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -29553,7 +29553,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -29568,7 +29568,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -29588,7 +29588,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -29603,7 +29603,7 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -29629,7 +29629,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4959</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29644,7 +29644,7 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29664,7 +29664,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8591</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29694,12 +29694,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29709,12 +29709,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -29775,7 +29775,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>3428</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29790,7 +29790,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29810,7 +29810,7 @@
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -29846,12 +29846,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>9476</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -29861,12 +29861,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -29881,12 +29881,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>10797</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -29896,12 +29896,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -29916,12 +29916,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>16439</t>
+          <t>16478</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -29936,7 +29936,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -29957,12 +29957,12 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>18200</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>32707</t>
+          <t>33198</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -29972,12 +29972,12 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -29992,12 +29992,12 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>26712</t>
+          <t>26907</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -30007,12 +30007,12 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -30027,12 +30027,12 @@
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>48095</t>
+          <t>48014</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>73042</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -30042,12 +30042,12 @@
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -30068,12 +30068,12 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>91543</t>
+          <t>90212</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>117446</t>
+          <t>115740</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -30083,49 +30083,49 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>131210</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>115297</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>145121</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>54,68%</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
           <t>60,47%</t>
         </is>
       </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>131210</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>115413</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>144540</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>54,68%</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>60,23%</t>
-        </is>
-      </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
           <t>296</t>
@@ -30138,12 +30138,12 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>216694</t>
+          <t>215412</t>
         </is>
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>256476</t>
+          <t>255025</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
@@ -30153,12 +30153,12 @@
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -30179,12 +30179,12 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>46828</t>
+          <t>47277</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>69162</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -30194,12 +30194,12 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
@@ -30214,12 +30214,12 @@
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>49660</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>77926</t>
+          <t>78583</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -30229,12 +30229,12 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -30249,12 +30249,12 @@
       </c>
       <c r="S67" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>102820</t>
         </is>
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>139082</t>
+          <t>139339</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -30264,12 +30264,12 @@
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
